--- a/不常用用户清洗-测试数据.xlsx
+++ b/不常用用户清洗-测试数据.xlsx
@@ -480,18 +480,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,35 +515,40 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>account</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>last_login_at</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>关联用例</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>T日预期status</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>预期结果说明</t>
         </is>
@@ -561,31 +567,36 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>R1命中: 无agent+未登录61天</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>r1over60@test.com</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>B-01</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>R1命中: 无agent+未登录61天, 进入预警期, T日复核仍命中→禁用</t>
         </is>
@@ -604,31 +615,36 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>R1边界: 无agent+未登录满60天</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>r1eq60@test.com</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>B-02</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>R1边界: 恰满60天(日期差&gt;=60)→禁用</t>
         </is>
@@ -647,31 +663,36 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>R1不命中: 无agent+未登录59天</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>r1_59d@test.com</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>B-03</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>R1边界: 59天&lt;60天→不禁用, 不进预警</t>
         </is>
@@ -690,31 +711,36 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>R1不命中: 无agent+最近1天登录</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>r1active@test.com</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>活跃用户: 昨天登录→不受影响</t>
         </is>
@@ -733,27 +759,32 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>R1命中: 从未登录+创建61天</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>r1never61@test.com</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>B-06</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>从未登录: 以创建时间为准, 创建61天→禁用</t>
         </is>
@@ -772,27 +803,32 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>R1不命中: 从未登录+创建59天</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>r1new59@test.com</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>B-07</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>新账号: 创建59天从未登录→不满60天不禁用</t>
         </is>
@@ -811,31 +847,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>R1不命中: 无agent+未登录59天</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
           <t>r1_59y@test.com</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>B-03</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>(补充)第59天昨日场景, 与U1003同结论</t>
         </is>
@@ -854,31 +895,36 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>R1命中: agent已全删+未登录61天</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>r1delall@test.com</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>B-05</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>R1命中: agent已全部删除视为无agent, 未登录61天→禁用</t>
         </is>
@@ -897,31 +943,36 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>R1不命中: agent已全删+最近5天登录</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
           <t>r1delact@test.com</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>B-05</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>agent已全删但5天前登录→不禁用</t>
         </is>
@@ -940,31 +991,36 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>R2命中: 单agent零调用+未登录61天</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
           <t>r2hit@test.com</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>C-01</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>R2命中: 单agent+180天无调用+61天未登录→禁用</t>
         </is>
@@ -983,31 +1039,36 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t>R2命中: 多agent全部零调用+未登录70天</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
           <t>r2m_all0@test.com</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>C-02</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>R2命中: 3个agent全部180天无调用→禁用</t>
         </is>
@@ -1026,31 +1087,36 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
+          <t>R2不命中: 多agent其一有调用+未登录70天</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
           <t>r2m_1act@test.com</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>C-03</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>R2不命中: 3个agent中1个在180天内有调用→不禁用</t>
         </is>
@@ -1069,31 +1135,36 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
+          <t>R2窗口边界: 调用在180天前</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
           <t>r2c180@test.com</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>C-04</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>R2窗口边界: 调用记录恰在180天前当天(待实现确认口径)</t>
         </is>
@@ -1112,31 +1183,36 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>R2不命中: 调用在179天前</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t>r2c179@test.com</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>C-05</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>R2窗口边界: 调用记录在179天前(窗口内)→有调用不禁用</t>
         </is>
@@ -1155,31 +1231,36 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>R2不命中: agent创建不足180天</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
           <t>r2new@test.com</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>C-06</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>agent创建仅90天: 不足180天观察期→不命中零调用</t>
         </is>
@@ -1198,31 +1279,36 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
+          <t>R2不命中: agent零调用但60天内登录</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
           <t>r2login@test.com</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>C-08</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>R2不命中: agent虽180天无调用但30天前登录→60天内有登录不禁用</t>
         </is>
@@ -1241,31 +1327,36 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t>R2命中: 下线agent零调用+未登录70天</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
           <t>r2offline@test.com</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>C-07</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>R2命中: 下线状态agent仍属于当前存量, 180天无调用→禁用(按确认口径)</t>
         </is>
@@ -1284,31 +1375,36 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
+          <t>R2不命中: 未登录90天但agent有调用</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
           <t>d03ok@test.com</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>D-03</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>有agent+90天未登录但agent在180天内有调用→不禁用</t>
         </is>
@@ -1327,31 +1423,36 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
+          <t>R2命中: 未登录61天+agent零调用</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
           <t>d02hit@test.com</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>D-02</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>组合命中: 61天未登录+180天零调用→禁用, 原因记R2</t>
         </is>
@@ -1370,31 +1471,36 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>预警回流: T-7后恢复登录</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
           <t>e07@test.com</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>E-07</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>T-7邮件后T-5恢复登录→T-3不发邮件, T日复核不命中, 不禁用(需在T-5日更新登录时间)</t>
         </is>
@@ -1413,31 +1519,36 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
+          <t>预警回流: T-3后产生调用</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
           <t>e08@test.com</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>E-08</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>T-3后T-1恢复活跃(需在T-1日写入调用记录)→T日实时复核取消禁用</t>
         </is>
@@ -1456,31 +1567,36 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
+          <t>邮件失败: 邮箱非法仍禁用</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
           <t>e12@test.com</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>E-12</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>邮箱非法: 邮件发送失败仍执行禁用, 失败原因需入库</t>
         </is>
@@ -1499,31 +1615,36 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
+          <t>邮件失败: 邮件服务异常仍禁用</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
           <t>e13@test.com</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>E-13</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="I25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>(操作型)邮件服务异常日触发: 该用户仍正常禁用</t>
         </is>
@@ -1542,31 +1663,36 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
+          <t>排除场景: 已禁用不重复处理</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
           <t>k06@test.com</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="G26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>K-06</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>已禁用用户: 不重复处理/不重复发邮件</t>
         </is>
@@ -1585,31 +1711,36 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
+          <t>排除场景: 已注销不参与清洗</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
           <t>k05@test.com</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="G27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>K-05</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="I27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>已注销用户(status=2): 不参与清洗, 状态保持</t>
         </is>
@@ -1628,31 +1759,36 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
+          <t>无白名单: 管理员命中仍禁用</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
           <t>j01admin@test.com</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>J-01</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>无白名单: 管理员账号命中规则同样禁用</t>
         </is>
@@ -1671,31 +1807,36 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
+          <t>无白名单: 付费客户命中仍禁用</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
           <t>j01paid@test.com</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>J-01</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>无白名单: 付费客户命中规则同样禁用</t>
         </is>
@@ -1714,31 +1855,36 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t>恢复场景: 管理员恢复禁用账号</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
           <t>i01@test.com</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="G30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>I-01</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>已禁用: 供管理员在用户管理执行恢复→status恢复, 可登录</t>
         </is>
@@ -1757,31 +1903,36 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>恢复场景: 重复恢复幂等</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
           <t>i04@test.com</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>I-04</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>已恢复后再次点击恢复: 状态保持正常, 无副作用</t>
         </is>
@@ -1800,31 +1951,36 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
+          <t>实时复核: 名单命中后T-1登录</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
           <t>f05@test.com</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>F-04</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>实时复核: 名单生成时命中, T-1日用户登录(需操作)→T日复核跳过, 不误禁</t>
         </is>
@@ -1843,31 +1999,36 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
+          <t>正常对照: status=1登录成功</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
           <t>g07@test.com</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>G-07</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>正常用户对照: status=1页面登录成功</t>
         </is>
@@ -1886,31 +2047,36 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
+          <t>失败登录: 仅失败记录按未登录判定</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
           <t>b08@test.com</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="I34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>仅失败登录记录不更新登录时间→按70天未登录禁用</t>
         </is>
@@ -3408,7 +3574,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3426,7 +3592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03 ~ 2026-09-05</t>
+          <t>2026-09-02 ~ 2026-09-04</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">

--- a/不常用用户清洗-测试数据.xlsx
+++ b/不常用用户清洗-测试数据.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>tc_e07_recover_t7</t>
+          <t>tc_e07_recover_t2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>预警回流: T-7后恢复登录</t>
+          <t>预警回流: T-2后恢复登录</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>T-7邮件后T-5恢复登录→T-3不发邮件, T日复核不命中, 不禁用(需在T-5日更新登录时间)</t>
+          <t>T-2发件后同日恢复登录→T-1不发第二封邮件, T日复核不命中, 不禁用(发件后执行UPDATE)</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>tc_e08_recover_t3</t>
+          <t>tc_e08_recover_t1</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>预警回流: T-3后产生调用</t>
+          <t>预警回流: T-1产生调用</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>T-3后T-1恢复活跃(需在T-1日写入调用记录)→T日实时复核取消禁用</t>
+          <t>T-1当日(第二封邮件发送后)写入调用记录→T日实时复核取消禁用</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>T-7</t>
+          <t>T-2</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -3528,7 +3528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3569,17 +3569,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>T-7（首次识别+第1封邮件）</t>
+          <t>T-2（首次识别+第1封邮件）</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>识别命中用户, 发送T-7邮件; E-01</t>
+          <t>导入全部数据, 触发清洗任务, 发送第1封邮件; E-01</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
@@ -3587,17 +3587,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>T-6 ~ T-4</t>
+          <t>T-2（发件后同日）</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02 ~ 2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>不发送任何邮件; E-03</t>
+          <t>U1020执行UPDATE last_login_at恢复登录(E-07); 非邮件档位日不发送(E-03)</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
@@ -3605,17 +3605,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>T-5（E-07操作日）</t>
+          <t>T-1（第2封邮件）</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>U1020登录, 更新last_login_at=d(5)</t>
+          <t>触发任务, 发送第2封邮件; U1020不应收到(E-07); 发件后INSERT U1021调用记录(E-08); UPDATE U1030登录(F-04)</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
@@ -3623,56 +3623,20 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>T-3（第2封邮件）</t>
+          <t>T（正式禁用日）</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>仍命中的用户发送T-3邮件; E-02; U1020不应收到</t>
+          <t>实时复核→禁用; 核对status与页面登录</t>
         </is>
       </c>
       <c r="D6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>T-1（E-08/F-04操作日）</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>U1021产生调用记录; U1030登录</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>T（正式禁用日）</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>实时复核→禁用; 核对status与页面登录</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4351,7 +4315,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>tc_e07_recover_t7</t>
+          <t>tc_e07_recover_t2</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4383,7 +4347,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>tc_e08_recover_t3</t>
+          <t>tc_e08_recover_t1</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
